--- a/data/trans_orig/IQ09_D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D_R-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2066,9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>839,66</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1323,24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>386,24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2274,11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1177,6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>877,13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>815,42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2141,12</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>986,77</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1106,25</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>489,56</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2066.904828844282</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>839.6561346794833</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1323.236095737174</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>386.2430489869751</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2274.111048861391</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1177.604987003443</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>877.1289682505947</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>815.4209033873238</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>2141.122905497922</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>986.7721305633273</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1106.254943061202</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>489.5631386907495</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>939,13; 3934,88</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>218,8; 1962,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>360,0; 2160,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>89,21; 1065,16</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>613,99; 5040,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>496,36; 3023,26</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>720,0; 1110,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>450,0; 1080,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1097,83; 3821,22</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>505,24; 1855,72</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>557,57; 1958,37</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>186,89; 971,8</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>939.1276226632751</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>218.7994438632173</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>89.21130522376433</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>613.9894074389882</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>496.356830289469</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1097.834627134606</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>505.2382971773507</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>557.5727419511115</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>186.7123060430704</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3934.875364402756</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1962.830677488809</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1065.161920718106</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>5040</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3023.256948985864</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1110</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>3821.216421885441</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>1855.720608665789</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1958.374504258333</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>969.3442855406631</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>932,92</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1010,51</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>813,29</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1960,28</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>529,61</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>741,66</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>598,25</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1180,62</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>782,75</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>888,68</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>713,56</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1635,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>423,28; 1790,22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>582,43; 1615,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>439,75; 1598,78</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1315,31; 2975,69</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>242,6; 955,34</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>482,72; 1087,25</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>275,39; 1486,46</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>554,81; 2124,65</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>451,74; 1377,79</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>624,03; 1254,44</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>450,2; 1177,31</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1124,23; 2344,87</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>932.9175655554536</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1010.5058505323</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>813.2933294907905</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1960.280817311201</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>529.6071488319959</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>741.6573016672052</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>598.2502537973462</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1180.62259408789</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>782.7486234833103</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>888.6825485145617</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>713.5595853872205</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1635.441396319824</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1056,09</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1318,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>940,85</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1351,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1234,91</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>244,74</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>710,16</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1457,68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1125,3</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>856,71</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>838,62</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1404,21</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>423.2838473294448</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>582.4303559975708</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>439.7504175127602</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1315.309651757583</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>242.6011552970935</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>482.7193666167606</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>275.3872981517235</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>554.8097190764541</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>451.7397457839867</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>624.033099959238</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>450.1991400010474</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>1124.232447060244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>290,9; 2085,16</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>289,42; 3758,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>414,63; 2099,51</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>364,62; 2460,03</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>482,35; 3600,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>40,03; 870,67</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>288,11; 1259,58</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>575,23; 2423,13</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>514,47; 1997,44</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252,41; 2358,58</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>464,28; 1521,75</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>714,49; 2122,06</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1790.219819220229</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1615.355354887851</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1598.781638824267</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2975.692241296313</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>955.3434075385856</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1087.249810187411</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1486.464138225158</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2124.647755201803</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1377.786900243098</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1254.435793991176</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1177.306705617502</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>2344.865102497371</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1140,05</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1015,57</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>878,68</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1548,94</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>948,85</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>766,17</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>644,63</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1224,52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1068,67</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>904,17</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>770,93</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1416,45</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1056.090426517713</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1318.109169718414</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>940.8499099037535</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1351.969038155607</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1234.906770825112</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>244.7421153886814</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>710.1628688507678</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1457.681499529902</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1125.298013666066</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>856.7141072994721</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>838.6236747972434</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1404.206933855166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>687,48; 1792,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>667,1; 1558,09</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>556,59; 1408,77</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1073,15; 2249,67</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>507,61; 1677,19</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>513,86; 1174,61</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>417,53; 1255,2</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>710,43; 1905,84</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>729,78; 1512,38</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>636,68; 1200,57</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>530,89; 1109,19</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1054,93; 1957,54</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>290.8990841165474</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>289.4244393094197</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>414.6308341999024</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>364.6155570085704</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>482.3507211576406</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>40.0257409012566</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>288.1095927233675</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>575.2338911657296</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>514.4743891231958</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>252.405099612147</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>464.2786419597769</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>714.4944163336204</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2085.156553439935</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3757.997611024894</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2099.50850686593</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2460.033319726248</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>870.665950145415</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1259.577575180035</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2423.130888756722</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1997.438323595907</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>2358.577357714887</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1521.747502150485</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>2122.061484251816</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1140.052331090635</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1015.572102988115</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>878.6814384510232</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1548.936425072869</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>948.8454535284831</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>766.167992932946</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>644.6346331759288</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1224.524897460577</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1068.672074903559</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>904.1696260003995</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>770.9292778379756</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1416.445268064866</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>687.4783662625334</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>667.0953950035024</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>556.5907179458264</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1073.152880172508</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>507.6127131815576</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>513.8647119367296</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>417.5331589457379</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>710.4256136466851</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>729.7814094032586</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>636.683035396911</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>530.894379708471</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1054.93426473185</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1792.193224790381</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1558.09463697483</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1408.771766777626</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2249.673011307639</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1677.189912112222</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1174.605140710644</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1255.196537176316</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1905.838597281182</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1512.383458756617</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1200.571417420908</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1109.185444747269</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1957.542433894739</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
